--- a/data/raw_results/lanupro_vocabulary_fatty_acids.xlsx
+++ b/data/raw_results/lanupro_vocabulary_fatty_acids.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SH\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my_github_projects\lanupro_vocabulary_2025\data\raw_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA4C997-6A61-4BB5-BB82-3691C5E79B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1414F64-FA78-44D3-9B44-C55B1F7ED516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{06EA7712-9BA5-4E3A-B464-81F94650D082}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="347">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -1077,6 +1077,9 @@
   </si>
   <si>
     <t>fatty acid concentration</t>
+  </si>
+  <si>
+    <t>test</t>
   </si>
 </sst>
 </file>
@@ -2359,13 +2362,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1E034C6-174E-4BD8-87DA-20B5D61D5D37}">
-  <dimension ref="A1:BX108"/>
+  <dimension ref="A1:BY108"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:76">
+    <row r="1" spans="1:77">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2594,8 +2597,11 @@
       <c r="BX1" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="2" spans="1:76">
+      <c r="BY1" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="2" spans="1:77">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2825,7 +2831,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:76">
+    <row r="3" spans="1:77">
       <c r="A3" s="1" t="s">
         <v>111</v>
       </c>
@@ -3055,7 +3061,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="4" spans="1:76">
+    <row r="4" spans="1:77">
       <c r="A4" s="1" t="s">
         <v>266</v>
       </c>
@@ -3279,7 +3285,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="5" spans="1:76">
+    <row r="5" spans="1:77">
       <c r="A5" s="1" t="s">
         <v>112</v>
       </c>
@@ -3287,7 +3293,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="6" spans="1:76">
+    <row r="6" spans="1:77">
       <c r="A6" s="1" t="s">
         <v>113</v>
       </c>
@@ -3295,7 +3301,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="7" spans="1:76" ht="43.2">
+    <row r="7" spans="1:77" ht="43.2">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -3525,7 +3531,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="8" spans="1:76">
+    <row r="8" spans="1:77">
       <c r="A8" s="1" t="s">
         <v>109</v>
       </c>
@@ -3755,42 +3761,42 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:76">
+    <row r="9" spans="1:77">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:76">
+    <row r="10" spans="1:77">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:76">
+    <row r="11" spans="1:77">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:76">
+    <row r="12" spans="1:77">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:76">
+    <row r="13" spans="1:77">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:76">
+    <row r="14" spans="1:77">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:76">
+    <row r="15" spans="1:77">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:76">
+    <row r="16" spans="1:77">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>

--- a/data/raw_results/lanupro_vocabulary_fatty_acids.xlsx
+++ b/data/raw_results/lanupro_vocabulary_fatty_acids.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my_github_projects\lanupro_vocabulary_2025\data\raw_results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1414F64-FA78-44D3-9B44-C55B1F7ED516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CABF3E8E-DACD-4B71-A3C4-0ED5E5021B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{06EA7712-9BA5-4E3A-B464-81F94650D082}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="345">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -379,12 +379,6 @@
   </si>
   <si>
     <t>atol_ontology_sample_type_meat</t>
-  </si>
-  <si>
-    <t>ATOL_0000650</t>
-  </si>
-  <si>
-    <t>ATOL_0005835</t>
   </si>
   <si>
     <t>level_xx</t>
@@ -2362,231 +2356,231 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1E034C6-174E-4BD8-87DA-20B5D61D5D37}">
-  <dimension ref="A1:BY108"/>
+  <dimension ref="A1:BX108"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:77">
+    <row r="1" spans="1:76">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>122</v>
       </c>
       <c r="C1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" t="s">
         <v>124</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>125</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>126</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>127</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>128</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>129</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>130</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>131</v>
-      </c>
-      <c r="K1" t="s">
-        <v>132</v>
       </c>
       <c r="L1" t="s">
         <v>133</v>
       </c>
       <c r="M1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="N1" t="s">
         <v>134</v>
       </c>
       <c r="O1" t="s">
+        <v>135</v>
+      </c>
+      <c r="P1" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q1" t="s">
         <v>136</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>137</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>140</v>
-      </c>
-      <c r="R1" t="s">
-        <v>138</v>
       </c>
       <c r="S1" t="s">
         <v>139</v>
       </c>
       <c r="T1" t="s">
+        <v>140</v>
+      </c>
+      <c r="U1" t="s">
         <v>141</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>142</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>143</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>144</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>145</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>146</v>
       </c>
       <c r="Z1" t="s">
         <v>147</v>
       </c>
       <c r="AA1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AB1" t="s">
         <v>150</v>
       </c>
       <c r="AC1" t="s">
+        <v>151</v>
+      </c>
+      <c r="AD1" t="s">
         <v>152</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>153</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
+        <v>146</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>149</v>
+      </c>
+      <c r="AH1" t="s">
         <v>154</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AI1" t="s">
         <v>155</v>
       </c>
-      <c r="AG1" t="s">
-        <v>148</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>151</v>
-      </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK1" t="s">
         <v>156</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>157</v>
       </c>
-      <c r="AK1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>158</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>159</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>160</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>161</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>162</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>163</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>164</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>165</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>166</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>167</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>168</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>169</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>170</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>171</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>172</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>173</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>174</v>
       </c>
       <c r="BC1" t="s">
         <v>175</v>
       </c>
       <c r="BD1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="BE1" t="s">
         <v>176</v>
       </c>
       <c r="BF1" t="s">
+        <v>177</v>
+      </c>
+      <c r="BG1" t="s">
         <v>178</v>
       </c>
-      <c r="BG1" t="s">
+      <c r="BH1" t="s">
         <v>179</v>
       </c>
-      <c r="BH1" t="s">
+      <c r="BI1" t="s">
         <v>180</v>
       </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>181</v>
-      </c>
-      <c r="BJ1" t="s">
-        <v>182</v>
       </c>
       <c r="BK1" t="s">
         <v>183</v>
       </c>
       <c r="BL1" t="s">
+        <v>184</v>
+      </c>
+      <c r="BM1" t="s">
         <v>185</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
+        <v>182</v>
+      </c>
+      <c r="BO1" t="s">
         <v>186</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BP1" t="s">
         <v>187</v>
       </c>
-      <c r="BO1" t="s">
-        <v>184</v>
-      </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>188</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>189</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" t="s">
+        <v>337</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>340</v>
+      </c>
+      <c r="BU1" t="s">
         <v>190</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>191</v>
-      </c>
-      <c r="BT1" t="s">
-        <v>339</v>
-      </c>
-      <c r="BU1" t="s">
-        <v>342</v>
       </c>
       <c r="BV1" t="s">
         <v>192</v>
@@ -2595,13 +2589,10 @@
         <v>194</v>
       </c>
       <c r="BX1" t="s">
-        <v>196</v>
-      </c>
-      <c r="BY1" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="2" spans="1:77">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="2" spans="1:76">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2827,453 +2818,447 @@
       <c r="BW2" t="s">
         <v>108</v>
       </c>
-      <c r="BX2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:77">
+    </row>
+    <row r="3" spans="1:76">
       <c r="A3" s="1" t="s">
         <v>111</v>
       </c>
       <c r="B3" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C3" t="s">
+        <v>266</v>
+      </c>
+      <c r="D3" t="s">
         <v>267</v>
-      </c>
-      <c r="D3" t="s">
-        <v>268</v>
       </c>
       <c r="E3" t="s">
         <v>269</v>
       </c>
       <c r="F3" t="s">
+        <v>270</v>
+      </c>
+      <c r="G3" t="s">
         <v>271</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>272</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
+        <v>282</v>
+      </c>
+      <c r="J3" t="s">
         <v>273</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>274</v>
       </c>
-      <c r="J3" t="s">
+      <c r="L3" t="s">
+        <v>283</v>
+      </c>
+      <c r="M3" t="s">
+        <v>275</v>
+      </c>
+      <c r="N3" t="s">
         <v>284</v>
       </c>
-      <c r="K3" t="s">
-        <v>275</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="O3" t="s">
         <v>276</v>
       </c>
-      <c r="M3" t="s">
+      <c r="P3" t="s">
         <v>285</v>
       </c>
-      <c r="N3" t="s">
+      <c r="Q3" t="s">
+        <v>286</v>
+      </c>
+      <c r="R3" t="s">
+        <v>287</v>
+      </c>
+      <c r="S3" t="s">
         <v>277</v>
       </c>
-      <c r="O3" t="s">
-        <v>286</v>
-      </c>
-      <c r="P3" t="s">
+      <c r="T3" t="s">
+        <v>288</v>
+      </c>
+      <c r="U3" t="s">
         <v>278</v>
       </c>
-      <c r="Q3" t="s">
-        <v>287</v>
-      </c>
-      <c r="R3" t="s">
-        <v>288</v>
-      </c>
-      <c r="S3" t="s">
+      <c r="V3" t="s">
         <v>289</v>
       </c>
-      <c r="T3" t="s">
+      <c r="W3" t="s">
+        <v>290</v>
+      </c>
+      <c r="X3" t="s">
+        <v>291</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>292</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>293</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>294</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>295</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>296</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>297</v>
+      </c>
+      <c r="AE3" t="s">
         <v>279</v>
       </c>
-      <c r="U3" t="s">
-        <v>290</v>
-      </c>
-      <c r="V3" t="s">
+      <c r="AF3" t="s">
+        <v>298</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>299</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>300</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>301</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>268</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>302</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>336</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>303</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>304</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>305</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>306</v>
+      </c>
+      <c r="AQ3" t="s">
+        <v>307</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>308</v>
+      </c>
+      <c r="AS3" t="s">
+        <v>309</v>
+      </c>
+      <c r="AT3" t="s">
+        <v>310</v>
+      </c>
+      <c r="AU3" t="s">
+        <v>311</v>
+      </c>
+      <c r="AV3" t="s">
+        <v>312</v>
+      </c>
+      <c r="AW3" t="s">
+        <v>313</v>
+      </c>
+      <c r="AX3" t="s">
+        <v>314</v>
+      </c>
+      <c r="AY3" t="s">
+        <v>315</v>
+      </c>
+      <c r="AZ3" t="s">
+        <v>316</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>317</v>
+      </c>
+      <c r="BB3" t="s">
+        <v>318</v>
+      </c>
+      <c r="BC3" t="s">
+        <v>319</v>
+      </c>
+      <c r="BD3" t="s">
         <v>280</v>
       </c>
-      <c r="W3" t="s">
-        <v>291</v>
-      </c>
-      <c r="X3" t="s">
-        <v>292</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>293</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>294</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>295</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>296</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>297</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>298</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>299</v>
-      </c>
-      <c r="AF3" t="s">
+      <c r="BE3" t="s">
+        <v>320</v>
+      </c>
+      <c r="BF3" t="s">
+        <v>321</v>
+      </c>
+      <c r="BG3" t="s">
+        <v>322</v>
+      </c>
+      <c r="BH3" t="s">
+        <v>323</v>
+      </c>
+      <c r="BI3" t="s">
+        <v>324</v>
+      </c>
+      <c r="BJ3" t="s">
+        <v>325</v>
+      </c>
+      <c r="BK3" t="s">
+        <v>326</v>
+      </c>
+      <c r="BL3" t="s">
+        <v>327</v>
+      </c>
+      <c r="BM3" t="s">
+        <v>328</v>
+      </c>
+      <c r="BN3" t="s">
         <v>281</v>
       </c>
-      <c r="AG3" t="s">
-        <v>300</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>301</v>
-      </c>
-      <c r="AI3" t="s">
-        <v>302</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>303</v>
-      </c>
-      <c r="AK3" t="s">
-        <v>270</v>
-      </c>
-      <c r="AL3" t="s">
-        <v>304</v>
-      </c>
-      <c r="AM3" t="s">
+      <c r="BO3" t="s">
+        <v>329</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>330</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>331</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>332</v>
+      </c>
+      <c r="BS3" t="s">
         <v>338</v>
       </c>
-      <c r="AN3" t="s">
-        <v>305</v>
-      </c>
-      <c r="AO3" t="s">
-        <v>306</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>307</v>
-      </c>
-      <c r="AQ3" t="s">
-        <v>308</v>
-      </c>
-      <c r="AR3" t="s">
-        <v>309</v>
-      </c>
-      <c r="AS3" t="s">
-        <v>310</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>311</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>312</v>
-      </c>
-      <c r="AV3" t="s">
-        <v>313</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>314</v>
-      </c>
-      <c r="AX3" t="s">
-        <v>315</v>
-      </c>
-      <c r="AY3" t="s">
-        <v>316</v>
-      </c>
-      <c r="AZ3" t="s">
-        <v>317</v>
-      </c>
-      <c r="BA3" t="s">
-        <v>318</v>
-      </c>
-      <c r="BB3" t="s">
-        <v>319</v>
-      </c>
-      <c r="BC3" t="s">
-        <v>320</v>
-      </c>
-      <c r="BD3" t="s">
-        <v>321</v>
-      </c>
-      <c r="BE3" t="s">
-        <v>282</v>
-      </c>
-      <c r="BF3" t="s">
-        <v>322</v>
-      </c>
-      <c r="BG3" t="s">
-        <v>323</v>
-      </c>
-      <c r="BH3" t="s">
-        <v>324</v>
-      </c>
-      <c r="BI3" t="s">
-        <v>325</v>
-      </c>
-      <c r="BJ3" t="s">
-        <v>326</v>
-      </c>
-      <c r="BK3" t="s">
-        <v>327</v>
-      </c>
-      <c r="BL3" t="s">
-        <v>328</v>
-      </c>
-      <c r="BM3" t="s">
-        <v>329</v>
-      </c>
-      <c r="BN3" t="s">
-        <v>330</v>
-      </c>
-      <c r="BO3" t="s">
-        <v>283</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>331</v>
-      </c>
-      <c r="BQ3" t="s">
-        <v>332</v>
-      </c>
-      <c r="BR3" t="s">
+      <c r="BT3" t="s">
+        <v>339</v>
+      </c>
+      <c r="BU3" t="s">
         <v>333</v>
       </c>
-      <c r="BS3" t="s">
+      <c r="BV3" t="s">
         <v>334</v>
       </c>
-      <c r="BT3" t="s">
-        <v>340</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>341</v>
-      </c>
-      <c r="BV3" t="s">
+      <c r="BW3" t="s">
         <v>335</v>
       </c>
-      <c r="BW3" t="s">
-        <v>336</v>
-      </c>
-      <c r="BX3" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="4" spans="1:77">
+    </row>
+    <row r="4" spans="1:76">
       <c r="A4" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E4" t="s">
+        <v>199</v>
+      </c>
+      <c r="F4" t="s">
+        <v>200</v>
+      </c>
+      <c r="G4" t="s">
+        <v>201</v>
+      </c>
+      <c r="H4" t="s">
+        <v>202</v>
+      </c>
+      <c r="I4" t="s">
+        <v>203</v>
+      </c>
+      <c r="J4" t="s">
+        <v>204</v>
+      </c>
+      <c r="K4" t="s">
+        <v>205</v>
+      </c>
+      <c r="L4" t="s">
+        <v>206</v>
+      </c>
+      <c r="M4" t="s">
+        <v>207</v>
+      </c>
+      <c r="N4" t="s">
+        <v>208</v>
+      </c>
+      <c r="O4" t="s">
+        <v>209</v>
+      </c>
+      <c r="P4" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>211</v>
+      </c>
+      <c r="R4" t="s">
+        <v>212</v>
+      </c>
+      <c r="S4" t="s">
+        <v>213</v>
+      </c>
+      <c r="T4" t="s">
+        <v>214</v>
+      </c>
+      <c r="U4" t="s">
+        <v>215</v>
+      </c>
+      <c r="V4" t="s">
+        <v>216</v>
+      </c>
+      <c r="W4" t="s">
+        <v>217</v>
+      </c>
+      <c r="X4" t="s">
+        <v>218</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>219</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>220</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>221</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>222</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>223</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>224</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>225</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>226</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>227</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>228</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>229</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>230</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>231</v>
+      </c>
+      <c r="AL4" t="s">
         <v>232</v>
       </c>
-      <c r="C4" t="s">
-        <v>198</v>
-      </c>
-      <c r="D4" t="s">
-        <v>199</v>
-      </c>
-      <c r="E4" t="s">
-        <v>200</v>
-      </c>
-      <c r="F4" t="s">
-        <v>201</v>
-      </c>
-      <c r="G4" t="s">
-        <v>202</v>
-      </c>
-      <c r="H4" t="s">
-        <v>203</v>
-      </c>
-      <c r="I4" t="s">
-        <v>204</v>
-      </c>
-      <c r="J4" t="s">
-        <v>205</v>
-      </c>
-      <c r="K4" t="s">
-        <v>206</v>
-      </c>
-      <c r="L4" t="s">
-        <v>207</v>
-      </c>
-      <c r="M4" t="s">
-        <v>208</v>
-      </c>
-      <c r="N4" t="s">
-        <v>209</v>
-      </c>
-      <c r="O4" t="s">
-        <v>210</v>
-      </c>
-      <c r="P4" t="s">
-        <v>211</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>212</v>
-      </c>
-      <c r="R4" t="s">
-        <v>213</v>
-      </c>
-      <c r="S4" t="s">
-        <v>214</v>
-      </c>
-      <c r="T4" t="s">
-        <v>215</v>
-      </c>
-      <c r="U4" t="s">
-        <v>216</v>
-      </c>
-      <c r="V4" t="s">
-        <v>217</v>
-      </c>
-      <c r="W4" t="s">
-        <v>218</v>
-      </c>
-      <c r="X4" t="s">
-        <v>219</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>220</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>221</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>222</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>223</v>
-      </c>
-      <c r="AC4" t="s">
-        <v>224</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>225</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>226</v>
-      </c>
-      <c r="AF4" t="s">
-        <v>227</v>
-      </c>
-      <c r="AG4" t="s">
-        <v>228</v>
-      </c>
-      <c r="AH4" t="s">
-        <v>229</v>
-      </c>
-      <c r="AI4" t="s">
-        <v>230</v>
-      </c>
-      <c r="AJ4" t="s">
-        <v>231</v>
-      </c>
-      <c r="AK4" t="s">
-        <v>232</v>
-      </c>
-      <c r="AL4" t="s">
+      <c r="AM4" t="s">
         <v>233</v>
       </c>
-      <c r="AM4" t="s">
+      <c r="AN4" t="s">
         <v>234</v>
       </c>
-      <c r="AN4" t="s">
+      <c r="AO4" t="s">
         <v>235</v>
       </c>
-      <c r="AO4" t="s">
+      <c r="AP4" t="s">
         <v>236</v>
       </c>
-      <c r="AP4" t="s">
+      <c r="AQ4" t="s">
         <v>237</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AR4" t="s">
         <v>238</v>
       </c>
-      <c r="AR4" t="s">
+      <c r="AS4" t="s">
         <v>239</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="AT4" t="s">
         <v>240</v>
       </c>
-      <c r="AT4" t="s">
+      <c r="AU4" t="s">
         <v>241</v>
       </c>
-      <c r="AU4" t="s">
+      <c r="AV4" t="s">
         <v>242</v>
       </c>
-      <c r="AV4" t="s">
+      <c r="AW4" t="s">
         <v>243</v>
       </c>
-      <c r="AW4" t="s">
+      <c r="AX4" t="s">
         <v>244</v>
       </c>
-      <c r="AX4" t="s">
+      <c r="AY4" t="s">
         <v>245</v>
       </c>
-      <c r="AY4" t="s">
+      <c r="AZ4" t="s">
         <v>246</v>
       </c>
-      <c r="AZ4" t="s">
+      <c r="BA4" t="s">
+        <v>253</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>254</v>
+      </c>
+      <c r="BC4" t="s">
+        <v>255</v>
+      </c>
+      <c r="BD4" t="s">
         <v>247</v>
       </c>
-      <c r="BA4" t="s">
+      <c r="BE4" t="s">
         <v>248</v>
       </c>
-      <c r="BB4" t="s">
-        <v>255</v>
-      </c>
-      <c r="BC4" t="s">
+      <c r="BF4" t="s">
+        <v>249</v>
+      </c>
+      <c r="BG4" t="s">
+        <v>250</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>251</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>251</v>
+      </c>
+      <c r="BJ4" t="s">
         <v>256</v>
       </c>
-      <c r="BD4" t="s">
+      <c r="BK4" t="s">
         <v>257</v>
       </c>
-      <c r="BE4" t="s">
-        <v>249</v>
-      </c>
-      <c r="BF4" t="s">
-        <v>250</v>
-      </c>
-      <c r="BG4" t="s">
-        <v>251</v>
-      </c>
-      <c r="BH4" t="s">
+      <c r="BL4" t="s">
+        <v>258</v>
+      </c>
+      <c r="BM4" t="s">
+        <v>259</v>
+      </c>
+      <c r="BN4" t="s">
         <v>252</v>
       </c>
-      <c r="BI4" t="s">
-        <v>253</v>
-      </c>
-      <c r="BJ4" t="s">
-        <v>253</v>
-      </c>
-      <c r="BK4" t="s">
-        <v>258</v>
-      </c>
-      <c r="BL4" t="s">
-        <v>259</v>
-      </c>
-      <c r="BM4" t="s">
+      <c r="BO4" t="s">
         <v>260</v>
       </c>
-      <c r="BN4" t="s">
+      <c r="BP4" t="s">
         <v>261</v>
       </c>
-      <c r="BO4" t="s">
-        <v>254</v>
-      </c>
-      <c r="BP4" t="s">
+      <c r="BQ4" t="s">
         <v>262</v>
       </c>
-      <c r="BQ4" t="s">
+      <c r="BR4" t="s">
         <v>263</v>
       </c>
-      <c r="BR4" t="s">
-        <v>264</v>
-      </c>
-      <c r="BS4" t="s">
-        <v>265</v>
+      <c r="BU4" t="s">
+        <v>191</v>
       </c>
       <c r="BV4" t="s">
         <v>193</v>
@@ -3281,257 +3266,245 @@
       <c r="BW4" t="s">
         <v>195</v>
       </c>
-      <c r="BX4" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="5" spans="1:77">
+    </row>
+    <row r="5" spans="1:76">
       <c r="A5" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B5" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="6" spans="1:77">
+    </row>
+    <row r="6" spans="1:76">
       <c r="A6" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B6" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="1:77" ht="43.2">
+    </row>
+    <row r="7" spans="1:76" ht="43.2">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="T7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="X7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="Y7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="Z7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AA7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AB7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AC7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AD7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AE7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AF7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AG7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AH7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AI7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AJ7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AK7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AL7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AM7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AN7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AO7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AP7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AQ7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AR7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AS7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AT7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AU7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AV7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AW7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AX7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AY7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AZ7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BA7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BB7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BC7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BD7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BE7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BF7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BG7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BH7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BI7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BJ7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BK7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BL7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BM7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BN7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BO7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BP7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BQ7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BR7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BS7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BT7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BU7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BV7" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="BW7" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="BX7" s="3" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="8" spans="1:77">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="8" spans="1:76">
       <c r="A8" s="1" t="s">
         <v>109</v>
       </c>
@@ -3757,46 +3730,43 @@
       <c r="BW8" t="s">
         <v>110</v>
       </c>
-      <c r="BX8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="9" spans="1:77">
+    </row>
+    <row r="9" spans="1:76">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:77">
+    <row r="10" spans="1:76">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:77">
+    <row r="11" spans="1:76">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:77">
+    <row r="12" spans="1:76">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:77">
+    <row r="13" spans="1:76">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:77">
+    <row r="14" spans="1:76">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:77">
+    <row r="15" spans="1:76">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:77">
+    <row r="16" spans="1:76">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -4270,7 +4240,7 @@
           <x14:formula1>
             <xm:f>description!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:BX2</xm:sqref>
+          <xm:sqref>B2:BW2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4323,7 +4293,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -4334,7 +4304,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -4349,7 +4319,7 @@
         <v>107</v>
       </c>
       <c r="H3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -4360,7 +4330,7 @@
         <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="57.6">
@@ -4371,7 +4341,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="57.6">
@@ -4382,7 +4352,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -4393,7 +4363,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -4404,18 +4374,18 @@
         <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B9" t="s">
         <v>5</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/data/raw_results/lanupro_vocabulary_fatty_acids.xlsx
+++ b/data/raw_results/lanupro_vocabulary_fatty_acids.xlsx
@@ -1,43 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my_github_projects\lanupro_vocabulary_2025\data\raw_results\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CABF3E8E-DACD-4B71-A3C4-0ED5E5021B94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{06EA7712-9BA5-4E3A-B464-81F94650D082}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="vocabulary" sheetId="3" r:id="rId1"/>
-    <sheet name="description" sheetId="2" r:id="rId2"/>
+    <sheet name="vocabulary" sheetId="3" state="visible" r:id="rId1"/>
+    <sheet name="description" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="416">
   <si>
     <t>lanupro_ontology</t>
   </si>
@@ -1074,33 +1051,230 @@
   </si>
   <si>
     <t>test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C4:0, 04:0, 4:0, c_04_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C5:0, 05:0, 5:0, c_05_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C6:0, 06:0, 6:0, c_06_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C7:0, 07:0, 7:0, c_07_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C8:0, 08:0, 8:0, c_08_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C9:0, 09:0, 9:0, c_09_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C10:0, 10:0, c_10_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C10:1, 10:1, C10.1, c_10_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C11:0, 11:0, c_11_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C12:0, 12:0, c_12_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C12:1, 12:1, C12.1, c_12_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C13:0, 13:0, c_13_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iso-C14:0, iso-C14.0, iso14:0, iso-14:0, iso_c_14_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C14:0, C14.0, 14:0, c_14_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C14:1, 14:1, C14.1, c_14_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iso-C15:0, iso-C15.0, iso15:0, iso-15:0, iso_c_15_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anteiso-C15:0, anteiso-C15.0, anteiso15:0, anteiso-15:0, anteiso_c_15_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C15:0, C15.0, 15:0, c_15_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iso-C16:0, iso-C16.0, iso16:0, iso-16:0, isoC16:0, iso_c_16_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C16:0, C16.0, 16:0, c_16_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t6/7/8-C16:1, trans-6/7/8-C16:1, t6/7/8C16:1, t6/7/8 16:1, trans6/7/8-C16:1, trans_6_plus_trans_7_plus_trans_8_c_16_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t9-C16:1, trans-9-C16:1, t9C16:1, t9 16:1, trans9-C16:1, trans_9_c_16_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t10-C16:1, trans-10-C16:1, t10C16:1, t10 16:1, trans10-C16:1, trans_10_c_16_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t11/12-C16:1, trans-11/12-C16:1, t11/12C16:1, t11/t12 16:1, t11/12 16:1, trans_11_plus_trans_12_c_16_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c7-C16:1, cis-7-C16:1, c7C16:1, c716:1, c7 16:1, cis_7_c_16_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c9-C16:1, cis-9-C16:1, c9C16:1, c916:1, c9 16:1, cis_9_c_16_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c11-C16:1, cis-11-C16:1, c11C16:1, c1116:1, c11 16:1, cis_11_c_16_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t14-C16:1, trans-14-C16:1, t14C16:1, t1416:1, t14 16:1, trans_14_c_16_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c13-C16:1, cis-13-C16:1, c13C16:1, c1316:1, c13 16:1, cis_13_c_16_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C17:0, C17.0, 17:0, c_17_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iso-C17:0, iso-C17.0, isoC17:0, iso17:0, iso-17:0, iso 17:0, iso_c_17_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anteiso-C17:0, anteiso-C17.0, anteisoC17:0, anteiso17:0, anteiso-17:0, anteiso 17:0, antiso17:0, anteiso_c_17_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iso-C17:0 + C16:1, iso-C17:0+C16:1, iso17:0+C16:1, iso 17:0 + c7/t11/12 16:1, iso_c_17_0_plus_cis_7_plus_trans_11_plus_trans_12_c_16_1, iso_c_17_0_plus_cis_7_c_16_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c9-C17:1, cis-9-C17:1, c9C17:1, c917:1, c9 17:1, cis_9_c_17_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C18:0, C18.0, 18:0, c_18_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iso-C18:0, iso-C18.0, isoC18:0, iso18:0, iso-18:0, iso 18:0, iso_c_18_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t6/7/8-C18:1, trans-6/7/8-C18:1, t6/7/8C18:1, t6/7/8 18:1, trans6/7/8-C18:1, t6/7/818:1, trans_6_plus_trans_7_plus_trans_8_c_18_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t9-C18:1, trans-9-C18:1, t9C18:1, t918:1, t9 18:1, trans9-C18:1, trans_9_c_18_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t10-C18:1, trans-10-C18:1, t10C18:1, t1018:1, t10 18:1, trans10-C18:1, trans_10_c_18_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t11-C18:1, trans-11-C18:1, t11C18:1, t1118:1, t11 18:1, trans11-C18:1, trans_11_c_18_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t12-C18:1, trans-12-C18:1, t12C18:1, t1218:1, t12 18:1, trans12-C18:1, trans_12_c_18_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c9/t13/14-C18:1, cis-9/trans-13/trans-14-C18:1, c9/t13/14C18:1, t13/14+c918:1, c9 + t13/14 18:1, c9 +t13/t14 18:1, cis_9_plus_trans_13_plus_trans_14_c_18_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c9/t12/13/14-C18:1, cis-9/trans-12/13/14-C18:1, c9/t12/13/14C18:1, t12/13/14+c918:1, c9 + t12/13/14 18:1, cis_9_plus_trans_12_plus_13_plus_trans_14_c_18_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t15-C18:1, trans-15-C18:1, t15C18:1, t1518:1, t15 18:1, trans15-C18:1, trans_15_c_18_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c11-C18:1, cis-11-C18:1, c11C18:1, c1118:1, c11 18:1, cis_11_c_18_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c12-C18:1, cis-12-C18:1, c12C18:1, c1218:1, c12 18:1, cis_12_c_18_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c13-C18:1, cis-13-C18:1, c13C18:1, c1318:1, c13 18:1, cis_13_c_18_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c14/t16-C18:1, cis-14/trans-16-C18:1, c14+t16C18:1, c14+t1618:1, c14/t16C18:1, c14+t16 18:1, cis_14_plus_trans_16_c_18_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c15-C18:1, cis-15-C18:1, c15C18:1, c1518:1, c15 18:1, cis_15_c_18_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLA (c9,t11), CLA c9,t11, cis-9 trans-11 CLA, CLAc9t11C18:2, CLAc9t1118:2, CLA c9t11 18:2, c9t11-CLA, cla_cis_9_trans_11_c_18_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t11,c15-C18:2, trans-11 cis-15-C18:2, t11c15C18:2, t11c1518:2, t11,c15 18:2, trans_11_cis_15_c_18_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C18:2n-6, C18:2 n-6, 18:2n-6, 18:2 n-6, n-6C18:2, n-618:2, n-6 18:2, n_6_c_18_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C18:3n-6, C18:3 n-6, 18:3n-6, 18:3 n-6, n-6C18:3, n-618:3, n-6 18:3, n_6_c_18_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C18:3n-3, C18:3 n-3, 18:3n-3, 18:3 n-3, n-3C18:3, n-318:3, n-3 18:3, n_3_c_18_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C20:0, C20.0, 20:0, c_20_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c7-C20:1, cis-7-C20:1, c7C20:1, c720:1, c7 20:1, cis_7_c_20_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c9-C20:1, cis-9-C20:1, c9C20:1, c920:1, c9 20:1, cis_9_c_20_1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLA (t10,c12), CLA t10,c12, trans-10 cis-12 CLA, CLAt10c12C18:2, CLAt10c1218:2, CLA t10,c12 18:2, t10c12-CLA, cla_trans_10_cis_12_c_18_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C20:1 + CLA, C20:1+CLA, C20:1 + CLA (c9,t11), c7+c9 20:1 + CLAc9,t11 18:2, cis_7_plus_cis_9_c_20_1_plus_cla_cis_9_trans_11_c_18_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C20:1 + CLA, C20:1+CLA, C20:1 + CLA (c9,t11), c7 20:1 + CLAc9,t11 18:2, cis_7_c_20_1_plus_cla_cis_9_trans_11_c_18_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C20:3n-6, C20:3 n-6, 20:3n-6, 20:3 n-6, n-6C20:3, n-620:3, n-6 20:3, n_6_c_20_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C20:3n-3, C20:3 n-3, 20:3n-3, 20:3 n-3, n-3C20:3, n-320:3, n-3 20:3, n_3_c_20_3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C20:4n-6, C20:4 n-6, 20:4n-6, 20:4 n-6, n-6C20:4, n-620:4, n-6 20:4, n_6_c_20_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C20:5n-3, C20:5 n-3, 20:5n-3, 20:5 n-3, n-3C20:5, n-320:5, n-3 20:5, n_3_c_20_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22:0, C22.0, 22:0, c_22_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22:4n-6, C22:4 n-6, 22:4n-6, 22:4 n-6, n-6C22:4, n-622:4, n-6 22:4, n_6_c_22_4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22:5n-6, C22:5 n-6, 22:5n-6, 22:5 n-6, n-6C22:5, n-622:5, n-6 22:5, n_6_c_22_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22:5n-3, C22:5 n-3, 22:5n-3, 22:5 n-3, n-3C22:5, n-322:5, n-3 22:5, n_3_c_22_5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22:6n-3, C22:6 n-3, 22:6n-3, 22:6 n-3, n-3C22:6, n-322:6, n-3 22:6, n_3_c_22_6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C24:0, c_24_0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C24:1, c_24_1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="37">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1111,454 +1285,23 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="52"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="9"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color indexed="23"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="17"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color indexed="56"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color indexed="56"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="56"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="52"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="60"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="63"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color indexed="56"/>
-      <name val="Cambria"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Aptos Display"/>
-      <family val="1"/>
-      <scheme val="major"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="20"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="62"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="22"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="55"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="43"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="26"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="45"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="42"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="47"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="20">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1566,341 +1309,9 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="23"/>
-      </left>
-      <right style="thin">
-        <color indexed="23"/>
-      </right>
-      <top style="thin">
-        <color indexed="23"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="23"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color indexed="63"/>
-      </left>
-      <right style="double">
-        <color indexed="63"/>
-      </right>
-      <top style="double">
-        <color indexed="63"/>
-      </top>
-      <bottom style="double">
-        <color indexed="63"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color indexed="52"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color indexed="62"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color indexed="22"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color indexed="30"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="22"/>
-      </left>
-      <right style="thin">
-        <color indexed="22"/>
-      </right>
-      <top style="thin">
-        <color indexed="22"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="22"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="63"/>
-      </left>
-      <right style="thin">
-        <color indexed="63"/>
-      </right>
-      <top style="thin">
-        <color indexed="63"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="63"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="62"/>
-      </top>
-      <bottom style="double">
-        <color indexed="62"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalDown="1">
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="112">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="36" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="35" fillId="39" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="36" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="34" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="19"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="19"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="19"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1908,123 +1319,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="112">
-    <cellStyle name="20% - Accent1 2" xfId="19" xr:uid="{77E55010-737E-41F1-998F-D4B5A5EBB76A}"/>
-    <cellStyle name="20% - Accent2 2" xfId="20" xr:uid="{5612D2A5-6A75-4CD7-9A73-3C984F0DD2F6}"/>
-    <cellStyle name="20% - Accent3 2" xfId="21" xr:uid="{1EE783BA-96F9-4646-BF0C-F8EBEFF4CA65}"/>
-    <cellStyle name="20% - Accent4 2" xfId="22" xr:uid="{774CDD67-E446-405A-A6C1-A44F5DD4F2CA}"/>
-    <cellStyle name="20% - Accent5 2" xfId="23" xr:uid="{9F17A24F-4B99-4600-A7D0-CB3EFC5F2D2F}"/>
-    <cellStyle name="20% - Accent6 2" xfId="24" xr:uid="{E4111880-B075-4613-A90E-D6F25D799BFF}"/>
-    <cellStyle name="40% - Accent1 2" xfId="25" xr:uid="{AB3CD54E-1153-49E7-B905-EE37264D0606}"/>
-    <cellStyle name="40% - Accent2 2" xfId="26" xr:uid="{7D90B17A-C500-4810-BD34-9DA9F9A2D0C4}"/>
-    <cellStyle name="40% - Accent3 2" xfId="27" xr:uid="{6B2AA50F-DC40-4FA7-89BD-9CDA01056B42}"/>
-    <cellStyle name="40% - Accent4 2" xfId="28" xr:uid="{C85E8DEA-11E4-44DE-9309-AA0C92ECB99C}"/>
-    <cellStyle name="40% - Accent5 2" xfId="29" xr:uid="{0D67FD36-E38A-46F7-B2FA-A533CB24D133}"/>
-    <cellStyle name="40% - Accent6 2" xfId="30" xr:uid="{027AFAE7-8D20-4E9C-A906-196A1421D135}"/>
-    <cellStyle name="60% - Accent1 2" xfId="31" xr:uid="{A12CCB9C-5C89-4076-92B8-AA4C203F0393}"/>
-    <cellStyle name="60% - Accent2 2" xfId="32" xr:uid="{EC4D8A80-456B-456F-B445-292696DA82D4}"/>
-    <cellStyle name="60% - Accent3 2" xfId="33" xr:uid="{95AD93C8-84F9-41C6-A4EB-7760DE9BF657}"/>
-    <cellStyle name="60% - Accent4 2" xfId="34" xr:uid="{A6EB875B-5865-4F70-AB71-1CEA3A701DAB}"/>
-    <cellStyle name="60% - Accent5 2" xfId="35" xr:uid="{3641AD94-8712-4C96-93D4-FB5E12EE9220}"/>
-    <cellStyle name="60% - Accent6 2" xfId="36" xr:uid="{80B20CC7-13B1-4963-B803-5D9CDB69F585}"/>
-    <cellStyle name="Accent1 2" xfId="50" xr:uid="{9B0D06FD-73A2-4659-9D64-2D0DD0F5AF07}"/>
-    <cellStyle name="Accent2 2" xfId="51" xr:uid="{D139D2E3-0712-4E42-8590-6A3DE1B16FB4}"/>
-    <cellStyle name="Accent3 2" xfId="52" xr:uid="{030C079C-076B-46CB-B4F4-83A96DDCAEBB}"/>
-    <cellStyle name="Accent4 2" xfId="53" xr:uid="{96E9A8BA-77D2-419E-B939-6952BFC48A05}"/>
-    <cellStyle name="Accent5 2" xfId="54" xr:uid="{0989281E-7380-4983-B026-5C8EDF224328}"/>
-    <cellStyle name="Accent6 2" xfId="55" xr:uid="{BDDCC53F-AD67-45FB-8B17-C3BEC3B0E993}"/>
-    <cellStyle name="Berekening 2" xfId="45" xr:uid="{5C241621-29C2-49A2-8068-B9AAF36D8CDE}"/>
-    <cellStyle name="Berekening 3" xfId="66" xr:uid="{785BFE43-5E7E-4D3F-9609-839D40BC7E6A}"/>
-    <cellStyle name="Berekening 4" xfId="2" xr:uid="{3ADEF913-B4ED-435D-9C2B-FF63DCAABC81}"/>
-    <cellStyle name="Controlecel 2" xfId="46" xr:uid="{40939F69-3B5E-4E0E-9C7F-7B0F9A78FA4E}"/>
-    <cellStyle name="Controlecel 2 2" xfId="67" xr:uid="{A4C20829-7350-48C9-8F02-4983197C300C}"/>
-    <cellStyle name="Controlecel 3" xfId="3" xr:uid="{40E1AD76-B68A-4875-8B66-806CB7C9ED2F}"/>
-    <cellStyle name="Gekoppelde cel 2" xfId="49" xr:uid="{86070388-3956-4C66-8664-61A95B0DE0FC}"/>
-    <cellStyle name="Gekoppelde cel 2 2" xfId="68" xr:uid="{609E685B-D294-4098-A53C-21ECAEC80FB1}"/>
-    <cellStyle name="Gekoppelde cel 3" xfId="4" xr:uid="{5C8785CF-A278-4895-8223-85AEA7BE2D2A}"/>
-    <cellStyle name="Goed 2" xfId="43" xr:uid="{8064DBF3-1DA3-4FE4-9A0D-3F61F44771D3}"/>
-    <cellStyle name="Goed 2 2" xfId="69" xr:uid="{FC68EE80-601A-45BB-A2F6-AA17BEE46EA8}"/>
-    <cellStyle name="Goed 3" xfId="60" xr:uid="{C36DB41B-71F9-4AE3-910B-B06CD90B76E6}"/>
-    <cellStyle name="Invoer 2" xfId="58" xr:uid="{48F80633-A8F5-4232-995C-11E08A985EAB}"/>
-    <cellStyle name="Invoer 2 2" xfId="70" xr:uid="{4E542AD0-A8D5-40B9-97A7-349100EA570F}"/>
-    <cellStyle name="Komma 2" xfId="90" xr:uid="{B81E1F0A-CB2B-4326-8DB8-E3DA63F080EB}"/>
-    <cellStyle name="Komma 2 2" xfId="105" xr:uid="{C36D3F85-4000-4D8F-A237-13B221CFA856}"/>
-    <cellStyle name="Komma 3" xfId="97" xr:uid="{4F054256-EE55-40E9-9FFD-52176700BDE7}"/>
-    <cellStyle name="Komma 3 2" xfId="108" xr:uid="{18E57360-1321-4074-ACFD-B97379C2750D}"/>
-    <cellStyle name="Komma 4" xfId="98" xr:uid="{2E7433BB-A755-48DE-B941-D1590D7527AD}"/>
-    <cellStyle name="Kop 1 2" xfId="38" xr:uid="{5D06AA92-C0EA-415F-B168-3359929941A0}"/>
-    <cellStyle name="Kop 1 2 2" xfId="71" xr:uid="{72B57CB9-8D4C-4181-8783-604270EB7E2C}"/>
-    <cellStyle name="Kop 1 3" xfId="5" xr:uid="{89970BEA-9B19-4167-B9B5-5B544E76D19C}"/>
-    <cellStyle name="Kop 2 2" xfId="39" xr:uid="{7A88F097-145E-4B00-B10E-A9F95E2063C7}"/>
-    <cellStyle name="Kop 2 2 2" xfId="72" xr:uid="{B36E6EEC-3466-410E-8F0E-64B75D7616C4}"/>
-    <cellStyle name="Kop 2 3" xfId="6" xr:uid="{95E371E1-CD9C-4030-BFED-7F431548C290}"/>
-    <cellStyle name="Kop 3 2" xfId="40" xr:uid="{31EF5F52-D190-48F1-B70F-D8F7EEA0505B}"/>
-    <cellStyle name="Kop 3 2 2" xfId="73" xr:uid="{B3E9B3F8-1824-4C40-B4CE-356A90FA5E74}"/>
-    <cellStyle name="Kop 3 3" xfId="7" xr:uid="{AB4819FB-ADDD-4E52-A98E-5A6853BB7A29}"/>
-    <cellStyle name="Kop 4 2" xfId="41" xr:uid="{D5D05C63-4752-40EA-87AD-5D3E6FF9E925}"/>
-    <cellStyle name="Kop 4 2 2" xfId="74" xr:uid="{9FC4EAC1-D178-4CBC-9CC6-F0DD1DB1DFED}"/>
-    <cellStyle name="Kop 4 3" xfId="8" xr:uid="{686D0746-3AB5-46CE-9505-FDB235318D2F}"/>
-    <cellStyle name="Neutraal 2" xfId="56" xr:uid="{1F16FDF9-D660-44BF-9DE5-4E9D809B013C}"/>
-    <cellStyle name="Neutraal 2 2" xfId="75" xr:uid="{AFBEA7E9-020C-4ECD-9F3A-BF8217DA1D81}"/>
-    <cellStyle name="Neutraal 3" xfId="9" xr:uid="{F6E6D1BC-195D-44F6-8385-15C01E3B71BF}"/>
-    <cellStyle name="Normal 2" xfId="61" xr:uid="{248692A6-8C4F-42E3-9CD9-77CC2AC4F1CC}"/>
-    <cellStyle name="Normal 3" xfId="62" xr:uid="{E7F4261D-A6FC-4B01-B72C-571FC0C42134}"/>
-    <cellStyle name="Normal_gas measurements 1st April" xfId="111" xr:uid="{374E9D91-12B1-4263-8DC5-AE5825DFD4C4}"/>
-    <cellStyle name="Notitie 2" xfId="59" xr:uid="{30E3489B-1173-4B86-AA14-47B27C70122C}"/>
-    <cellStyle name="Notitie 2 2" xfId="76" xr:uid="{50D4571F-395A-4265-BA5E-F3AD2E420395}"/>
-    <cellStyle name="Notitie 3" xfId="10" xr:uid="{A8EE6992-94FA-4519-8DDF-2E0F62FFCABC}"/>
-    <cellStyle name="Ongeldig 2" xfId="42" xr:uid="{EFD29878-6CA6-4897-8789-988F52B3CF1C}"/>
-    <cellStyle name="Ongeldig 2 2" xfId="77" xr:uid="{D906DD6A-4D4D-4580-A704-8F20969B155E}"/>
-    <cellStyle name="Percent 2" xfId="109" xr:uid="{D8741785-D3C5-4F04-8E7B-57868EFAF623}"/>
-    <cellStyle name="Procent 2" xfId="89" xr:uid="{7E2E8C86-11C1-4651-9F27-363CECA4962E}"/>
-    <cellStyle name="Procent 2 2" xfId="104" xr:uid="{0A612F57-3FE7-4402-9BE7-20AB5ED4B43E}"/>
-    <cellStyle name="Procent 3" xfId="87" xr:uid="{F9E9FDD3-7184-4473-AB3A-F76148606F27}"/>
-    <cellStyle name="Procent 4" xfId="96" xr:uid="{CFA3823E-621B-4C54-8D94-D25422944FA1}"/>
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
-    <cellStyle name="Standaard 2" xfId="16" xr:uid="{96A1B9A1-68B0-47BC-9C07-510AF0DABD7A}"/>
-    <cellStyle name="Standaard 2 2" xfId="85" xr:uid="{F4492B4C-450B-4576-90B0-D020096D8961}"/>
-    <cellStyle name="Standaard 2 2 2" xfId="101" xr:uid="{05FB0B07-87BE-4F3B-A0F0-470C04CF35E6}"/>
-    <cellStyle name="Standaard 2 3" xfId="94" xr:uid="{AF36A432-9881-4E49-A496-CD9DC2640CB5}"/>
-    <cellStyle name="Standaard 2 4" xfId="64" xr:uid="{E6860B40-5E59-4990-9314-CCF91B28A469}"/>
-    <cellStyle name="Standaard 3" xfId="17" xr:uid="{A46A9956-5BCC-4DC4-A258-FB797B591ADD}"/>
-    <cellStyle name="Standaard 3 2" xfId="86" xr:uid="{67BAD83C-2C10-490D-9DE6-D043A49F8D21}"/>
-    <cellStyle name="Standaard 3 2 2" xfId="102" xr:uid="{636288F9-DE61-48E9-843F-5A39CC315312}"/>
-    <cellStyle name="Standaard 3 3" xfId="95" xr:uid="{0D48C029-A2F0-4D9F-9198-6A424F2DEC94}"/>
-    <cellStyle name="Standaard 3 3 2" xfId="110" xr:uid="{7816AC37-F506-49B2-90FD-E05AD3AA2D6E}"/>
-    <cellStyle name="Standaard 3 4" xfId="83" xr:uid="{87E1DA24-3A8E-4733-ACE9-F2CD5EB5F086}"/>
-    <cellStyle name="Standaard 4" xfId="18" xr:uid="{657B3152-F744-456D-9286-7189D2044F5E}"/>
-    <cellStyle name="Standaard 4 2" xfId="63" xr:uid="{672A6526-EA11-4B56-BC62-D1C8904CDF6C}"/>
-    <cellStyle name="Standaard 4 2 2" xfId="99" xr:uid="{22A204D2-98C4-4AA1-91DF-03245CAB440F}"/>
-    <cellStyle name="Standaard 4 3" xfId="100" xr:uid="{2188E224-3A05-4608-B105-C18C5DC66621}"/>
-    <cellStyle name="Standaard 4 4" xfId="84" xr:uid="{D433F97C-5B93-4879-BC48-6C7BD1740436}"/>
-    <cellStyle name="Standaard 5" xfId="88" xr:uid="{F30789E1-BA89-4874-AC7A-A44718F58AD6}"/>
-    <cellStyle name="Standaard 5 2" xfId="103" xr:uid="{F70A4429-DB29-459B-B7BB-ADB8F0CB20B8}"/>
-    <cellStyle name="Standaard 6" xfId="91" xr:uid="{E66DDB15-0C54-49C6-914F-1AF380349C08}"/>
-    <cellStyle name="Standaard 6 2" xfId="92" xr:uid="{D31EB734-ED8B-4D5A-9E08-74A5419FB42D}"/>
-    <cellStyle name="Standaard 6 3" xfId="106" xr:uid="{C54C5384-E24F-40E5-B247-76E2A6106B35}"/>
-    <cellStyle name="Standaard 7" xfId="65" xr:uid="{E34ED3BB-96CB-43FB-B2E3-E6F18A7E2246}"/>
-    <cellStyle name="Standaard 8" xfId="93" xr:uid="{EDE193C4-BE47-4645-B8BB-669975AEF0C9}"/>
-    <cellStyle name="Standaard 8 2" xfId="107" xr:uid="{7856E6DD-949B-448A-AFC9-4DA647FC7B9A}"/>
-    <cellStyle name="Standaard 9" xfId="1" xr:uid="{FEBBD5E3-71E0-40E9-B054-D2EAD175178E}"/>
-    <cellStyle name="Titel 2" xfId="37" xr:uid="{2142A103-E0F1-47C0-8E08-B44D6706ADC6}"/>
-    <cellStyle name="Titel 2 2" xfId="78" xr:uid="{EDBE8CFE-106F-4D21-8E11-EECCFABFB22E}"/>
-    <cellStyle name="Titel 3" xfId="11" xr:uid="{D5629DD0-0D31-461D-8A80-5EC8C5B92BBD}"/>
-    <cellStyle name="Totaal 2" xfId="44" xr:uid="{1CF3E4F0-9433-4825-86D2-3BD6AE2857E0}"/>
-    <cellStyle name="Totaal 2 2" xfId="79" xr:uid="{0ABFFBCE-8C9F-4737-9265-817539C12D92}"/>
-    <cellStyle name="Totaal 3" xfId="12" xr:uid="{B7C7C850-EF17-45CA-927B-5EB272C0B3EF}"/>
-    <cellStyle name="Uitvoer 2" xfId="57" xr:uid="{59035552-E022-4BE1-B218-D6AE1AE7D833}"/>
-    <cellStyle name="Uitvoer 2 2" xfId="80" xr:uid="{2513F153-C1B3-4967-8357-DEC8813AEA4B}"/>
-    <cellStyle name="Uitvoer 3" xfId="13" xr:uid="{BBA66EC4-2682-4F4A-8D87-8C0C4E5CAEF3}"/>
-    <cellStyle name="Verklarende tekst 2" xfId="47" xr:uid="{9EF85BDA-038E-47FE-82F8-3C3CC97A91E6}"/>
-    <cellStyle name="Verklarende tekst 2 2" xfId="81" xr:uid="{E4B70EE5-9AD1-4912-BDF7-1E501CF827C1}"/>
-    <cellStyle name="Verklarende tekst 3" xfId="14" xr:uid="{85941920-41F1-4568-911D-8C02167790BD}"/>
-    <cellStyle name="Waarschuwingstekst 2" xfId="48" xr:uid="{964B1248-801D-4130-A435-585A835F7EF7}"/>
-    <cellStyle name="Waarschuwingstekst 2 2" xfId="82" xr:uid="{1EE91596-D9F5-4C3D-9515-B6C4CB1C6851}"/>
-    <cellStyle name="Waarschuwingstekst 3" xfId="15" xr:uid="{79F06BF8-8F3D-411A-AB0E-5D64168AEC1C}"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2355,14 +1655,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1E034C6-174E-4BD8-87DA-20B5D61D5D37}">
-  <dimension ref="A1:BX108"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:76">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2592,7 +1892,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="2" spans="1:76">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -2819,222 +2119,222 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:76">
+    <row r="3">
       <c r="A3" s="1" t="s">
         <v>111</v>
       </c>
       <c r="B3" t="s">
-        <v>265</v>
+        <v>345</v>
       </c>
       <c r="C3" t="s">
-        <v>266</v>
+        <v>346</v>
       </c>
       <c r="D3" t="s">
-        <v>267</v>
+        <v>347</v>
       </c>
       <c r="E3" t="s">
-        <v>269</v>
+        <v>348</v>
       </c>
       <c r="F3" t="s">
-        <v>270</v>
+        <v>349</v>
       </c>
       <c r="G3" t="s">
-        <v>271</v>
+        <v>350</v>
       </c>
       <c r="H3" t="s">
-        <v>272</v>
+        <v>351</v>
       </c>
       <c r="I3" t="s">
-        <v>282</v>
+        <v>352</v>
       </c>
       <c r="J3" t="s">
-        <v>273</v>
+        <v>353</v>
       </c>
       <c r="K3" t="s">
-        <v>274</v>
+        <v>354</v>
       </c>
       <c r="L3" t="s">
-        <v>283</v>
+        <v>355</v>
       </c>
       <c r="M3" t="s">
-        <v>275</v>
+        <v>356</v>
       </c>
       <c r="N3" t="s">
-        <v>284</v>
+        <v>357</v>
       </c>
       <c r="O3" t="s">
-        <v>276</v>
+        <v>358</v>
       </c>
       <c r="P3" t="s">
-        <v>285</v>
+        <v>359</v>
       </c>
       <c r="Q3" t="s">
-        <v>286</v>
+        <v>360</v>
       </c>
       <c r="R3" t="s">
-        <v>287</v>
+        <v>361</v>
       </c>
       <c r="S3" t="s">
-        <v>277</v>
+        <v>362</v>
       </c>
       <c r="T3" t="s">
-        <v>288</v>
+        <v>363</v>
       </c>
       <c r="U3" t="s">
-        <v>278</v>
+        <v>364</v>
       </c>
       <c r="V3" t="s">
-        <v>289</v>
+        <v>365</v>
       </c>
       <c r="W3" t="s">
-        <v>290</v>
+        <v>366</v>
       </c>
       <c r="X3" t="s">
-        <v>291</v>
+        <v>367</v>
       </c>
       <c r="Y3" t="s">
-        <v>292</v>
+        <v>368</v>
       </c>
       <c r="Z3" t="s">
-        <v>293</v>
+        <v>369</v>
       </c>
       <c r="AA3" t="s">
-        <v>294</v>
+        <v>370</v>
       </c>
       <c r="AB3" t="s">
-        <v>295</v>
+        <v>371</v>
       </c>
       <c r="AC3" t="s">
-        <v>296</v>
+        <v>372</v>
       </c>
       <c r="AD3" t="s">
-        <v>297</v>
+        <v>373</v>
       </c>
       <c r="AE3" t="s">
-        <v>279</v>
+        <v>374</v>
       </c>
       <c r="AF3" t="s">
-        <v>298</v>
+        <v>375</v>
       </c>
       <c r="AG3" t="s">
-        <v>299</v>
+        <v>376</v>
       </c>
       <c r="AH3" t="s">
-        <v>300</v>
+        <v>377</v>
       </c>
       <c r="AI3" t="s">
-        <v>301</v>
+        <v>378</v>
       </c>
       <c r="AJ3" t="s">
-        <v>268</v>
+        <v>379</v>
       </c>
       <c r="AK3" t="s">
-        <v>302</v>
+        <v>380</v>
       </c>
       <c r="AL3" t="s">
-        <v>336</v>
+        <v>381</v>
       </c>
       <c r="AM3" t="s">
-        <v>303</v>
+        <v>382</v>
       </c>
       <c r="AN3" t="s">
-        <v>304</v>
+        <v>383</v>
       </c>
       <c r="AO3" t="s">
-        <v>305</v>
+        <v>384</v>
       </c>
       <c r="AP3" t="s">
-        <v>306</v>
+        <v>385</v>
       </c>
       <c r="AQ3" t="s">
-        <v>307</v>
+        <v>386</v>
       </c>
       <c r="AR3" t="s">
-        <v>308</v>
+        <v>387</v>
       </c>
       <c r="AS3" t="s">
-        <v>309</v>
+        <v>388</v>
       </c>
       <c r="AT3" t="s">
-        <v>310</v>
+        <v>389</v>
       </c>
       <c r="AU3" t="s">
-        <v>311</v>
+        <v>390</v>
       </c>
       <c r="AV3" t="s">
-        <v>312</v>
+        <v>391</v>
       </c>
       <c r="AW3" t="s">
-        <v>313</v>
+        <v>392</v>
       </c>
       <c r="AX3" t="s">
-        <v>314</v>
+        <v>393</v>
       </c>
       <c r="AY3" t="s">
-        <v>315</v>
+        <v>394</v>
       </c>
       <c r="AZ3" t="s">
-        <v>316</v>
+        <v>395</v>
       </c>
       <c r="BA3" t="s">
-        <v>317</v>
+        <v>396</v>
       </c>
       <c r="BB3" t="s">
-        <v>318</v>
+        <v>397</v>
       </c>
       <c r="BC3" t="s">
-        <v>319</v>
+        <v>398</v>
       </c>
       <c r="BD3" t="s">
-        <v>280</v>
+        <v>399</v>
       </c>
       <c r="BE3" t="s">
-        <v>320</v>
+        <v>400</v>
       </c>
       <c r="BF3" t="s">
-        <v>321</v>
+        <v>401</v>
       </c>
       <c r="BG3" t="s">
-        <v>322</v>
+        <v>402</v>
       </c>
       <c r="BH3" t="s">
-        <v>323</v>
+        <v>403</v>
       </c>
       <c r="BI3" t="s">
-        <v>324</v>
+        <v>404</v>
       </c>
       <c r="BJ3" t="s">
-        <v>325</v>
+        <v>405</v>
       </c>
       <c r="BK3" t="s">
-        <v>326</v>
+        <v>406</v>
       </c>
       <c r="BL3" t="s">
-        <v>327</v>
+        <v>407</v>
       </c>
       <c r="BM3" t="s">
-        <v>328</v>
+        <v>408</v>
       </c>
       <c r="BN3" t="s">
-        <v>281</v>
+        <v>409</v>
       </c>
       <c r="BO3" t="s">
-        <v>329</v>
+        <v>410</v>
       </c>
       <c r="BP3" t="s">
-        <v>330</v>
+        <v>411</v>
       </c>
       <c r="BQ3" t="s">
-        <v>331</v>
+        <v>412</v>
       </c>
       <c r="BR3" t="s">
-        <v>332</v>
+        <v>413</v>
       </c>
       <c r="BS3" t="s">
-        <v>338</v>
+        <v>414</v>
       </c>
       <c r="BT3" t="s">
-        <v>339</v>
+        <v>415</v>
       </c>
       <c r="BU3" t="s">
         <v>333</v>
@@ -3046,7 +2346,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="4" spans="1:76">
+    <row r="4">
       <c r="A4" s="1" t="s">
         <v>264</v>
       </c>
@@ -3267,17 +2567,17 @@
         <v>195</v>
       </c>
     </row>
-    <row r="5" spans="1:76">
+    <row r="5">
       <c r="A5" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="6" spans="1:76">
+    <row r="6">
       <c r="A6" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="7" spans="1:76" ht="43.2">
+    <row r="7" ht="43.2" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>4</v>
       </c>
@@ -3504,7 +2804,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="8" spans="1:76">
+    <row r="8">
       <c r="A8" s="1" t="s">
         <v>109</v>
       </c>
@@ -3731,508 +3031,509 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="1:76">
+    <row r="9">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:76">
+    <row r="10">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:76">
+    <row r="11">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:76">
+    <row r="12">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:76">
+    <row r="13">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:76">
+    <row r="14">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:76">
+    <row r="15">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:76">
+    <row r="16">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25">
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28">
       <c r="A28" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29">
       <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30">
       <c r="A30" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31">
       <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32">
       <c r="A32" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33">
       <c r="A33" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34">
       <c r="A34" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35">
       <c r="A35" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36">
       <c r="A36" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37">
       <c r="A37" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38">
       <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39">
       <c r="A39" s="1" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40">
       <c r="A40" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41">
       <c r="A41" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42">
       <c r="A42" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43">
       <c r="A43" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44">
       <c r="A44" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45">
       <c r="A45" s="1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46">
       <c r="A46" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47">
       <c r="A47" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48">
       <c r="A48" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49">
       <c r="A49" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50">
       <c r="A50" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51">
       <c r="A51" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52">
       <c r="A52" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53">
       <c r="A53" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54">
       <c r="A54" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55">
       <c r="A55" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56">
       <c r="A56" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57">
       <c r="A57" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58">
       <c r="A58" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59">
       <c r="A59" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60">
       <c r="A60" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61">
       <c r="A61" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:1">
+    <row r="62">
       <c r="A62" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="1:1">
+    <row r="63">
       <c r="A63" s="1" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:1">
+    <row r="64">
       <c r="A64" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65">
       <c r="A65" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66">
       <c r="A66" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67">
       <c r="A67" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68">
       <c r="A68" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69">
       <c r="A69" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70">
       <c r="A70" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:1">
+    <row r="71">
       <c r="A71" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:1">
+    <row r="72">
       <c r="A72" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:1">
+    <row r="73">
       <c r="A73" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="74" spans="1:1">
+    <row r="74">
       <c r="A74" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="75" spans="1:1">
+    <row r="75">
       <c r="A75" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="76" spans="1:1">
+    <row r="76">
       <c r="A76" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="77" spans="1:1">
+    <row r="77">
       <c r="A77" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="78" spans="1:1">
+    <row r="78">
       <c r="A78" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="79" spans="1:1">
+    <row r="79">
       <c r="A79" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="80" spans="1:1">
+    <row r="80">
       <c r="A80" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="81" spans="1:1">
+    <row r="81">
       <c r="A81" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="82" spans="1:1">
+    <row r="82">
       <c r="A82" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="83" spans="1:1">
+    <row r="83">
       <c r="A83" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="1:1">
+    <row r="84">
       <c r="A84" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="85" spans="1:1">
+    <row r="85">
       <c r="A85" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="86" spans="1:1">
+    <row r="86">
       <c r="A86" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="87" spans="1:1">
+    <row r="87">
       <c r="A87" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="88" spans="1:1">
+    <row r="88">
       <c r="A88" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="89" spans="1:1">
+    <row r="89">
       <c r="A89" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
+    <row r="90">
       <c r="A90" s="1" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
+    <row r="91">
       <c r="A91" s="1" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
+    <row r="92">
       <c r="A92" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
+    <row r="93">
       <c r="A93" s="1" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
+    <row r="94">
       <c r="A94" s="1" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
+    <row r="95">
       <c r="A95" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
+    <row r="96">
       <c r="A96" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="97" spans="1:1">
+    <row r="97">
       <c r="A97" s="1" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="98" spans="1:1">
+    <row r="98">
       <c r="A98" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="99" spans="1:1">
+    <row r="99">
       <c r="A99" s="1" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="100" spans="1:1">
+    <row r="100">
       <c r="A100" s="1" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="101" spans="1:1">
+    <row r="101">
       <c r="A101" s="1" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="102" spans="1:1">
+    <row r="102">
       <c r="A102" s="1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="103" spans="1:1">
+    <row r="103">
       <c r="A103" s="1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="104" spans="1:1">
+    <row r="104">
       <c r="A104" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="105" spans="1:1">
+    <row r="105">
       <c r="A105" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="106" spans="1:1">
+    <row r="106">
       <c r="A106" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="107" spans="1:1">
+    <row r="107">
       <c r="A107" s="1" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="108" spans="1:1">
+    <row r="108">
       <c r="A108" s="1" t="s">
         <v>106</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
@@ -4249,17 +3550,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A68D4BA7-81A7-496D-83F7-4CE2A3B40B1B}">
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="27.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.44140625" customWidth="1"/>
-    <col min="3" max="3" width="80.44140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.5546875" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="80.44140625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -4285,7 +3586,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -4296,7 +3597,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -4322,7 +3623,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4">
       <c r="A4" t="s">
         <v>111</v>
       </c>
@@ -4333,7 +3634,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="57.6">
+    <row r="5" ht="57.6" customHeight="1">
       <c r="A5" t="s">
         <v>112</v>
       </c>
@@ -4344,7 +3645,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="57.6">
+    <row r="6" ht="57.6" customHeight="1">
       <c r="A6" t="s">
         <v>113</v>
       </c>
@@ -4355,7 +3656,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -4366,7 +3667,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8">
       <c r="A8" t="s">
         <v>109</v>
       </c>
@@ -4377,7 +3678,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9">
       <c r="A9" t="s">
         <v>114</v>
       </c>
@@ -4389,7 +3690,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>